--- a/medical_surveys_questionnaires/036_health_ai_explainability_awareness_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/036_health_ai_explainability_awareness_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_positive',_'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very Positive', 'label': 'Very Positive'}</t>
+          <t>Very Positive</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'positive',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Positive', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_negative',_'label':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Very Negative', 'label': 'Very Negative'}</t>
+          <t>Very Negative</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'very_low',_'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Very Low', 'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'very_high',_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Very High', 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_important',_'label':_'not_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Not Important', 'label': 'Not Important'}</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'important',_'label':_'important'}</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Important', 'label': 'Important'}</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Very Important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'frequently',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'always',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Always', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'frequently',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'always',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Always', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'effectiveness',_'label':_'effectiveness'}</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Effectiveness', 'label': 'Effectiveness'}</t>
+          <t>Effectiveness</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'safety',_'label':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Safety', 'label': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'efficiency',_'label':_'efficiency'}</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Efficiency', 'label': 'Efficiency'}</t>
+          <t>Efficiency</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'cost',_'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Cost', 'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'others',_'label':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Others', 'label': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'not_sure',_'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Not Sure', 'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'not_sure',_'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Not Sure', 'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'explain_in_detail',_'label':_'explain_in_detail'}</t>
+          <t>explain_in_detail</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Explain in detail', 'label': 'Explain in detail'}</t>
+          <t>Explain in detail</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'briefly_explain',_'label':_'briefly_explain'}</t>
+          <t>briefly_explain</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Briefly explain', 'label': 'Briefly explain'}</t>
+          <t>Briefly explain</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'no_explanation_needed',_'label':_'no_explanation_needed'}</t>
+          <t>no_explanation_needed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'No explanation needed', 'label': 'No explanation needed'}</t>
+          <t>No explanation needed</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_"don't_need_explanation",_'label':_"don't_need_explanation"}</t>
+          <t>don't_need_explanation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': "Don't need explanation", 'label': "Don't need explanation"}</t>
+          <t>Don't need explanation</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'text',_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Text', 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'images',_'label':_'images'}</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Images', 'label': 'Images'}</t>
+          <t>Images</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'videos',_'label':_'videos'}</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Videos', 'label': 'Videos'}</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'effective_in_treating_condition',_'label':_'effective_in_treating_condition'}</t>
+          <t>effective_in_treating_condition</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Effective in treating condition', 'label': 'Effective in treating condition'}</t>
+          <t>Effective in treating condition</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'easy_to_understand',_'label':_'easy_to_understand'}</t>
+          <t>easy_to_understand</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Easy to understand', 'label': 'Easy to understand'}</t>
+          <t>Easy to understand</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'cost-effective',_'label':_'cost-effective'}</t>
+          <t>cost-effective</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Cost-effective', 'label': 'Cost-effective'}</t>
+          <t>Cost-effective</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1775,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'others',_'label':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Others', 'label': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'effectiveness',_'label':_'effectiveness'}</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Effectiveness', 'label': 'Effectiveness'}</t>
+          <t>Effectiveness</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'safety',_'label':_'safety'}</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Safety', 'label': 'Safety'}</t>
+          <t>Safety</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'efficiency',_'label':_'efficiency'}</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Efficiency', 'label': 'Efficiency'}</t>
+          <t>Efficiency</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'cost',_'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Cost', 'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'others',_'label':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Others', 'label': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'not_recommended',_'label':_'not_recommended'}</t>
+          <t>not_recommended</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Not recommended', 'label': 'Not recommended'}</t>
+          <t>Not recommended</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'not_sure',_'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Not Sure', 'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
